--- a/data_extactor/batch_10_fa/batch_0057_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0057_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن‌گفتن | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | چالاکی دست | حساسیت به مشکل | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | وضوح گفتار | قدرت بالاتنه | دقت کنترل | چالاکی انگشتان | ثبات دست و بازو | تقسیم زمان</t>
+          <t>بینایی نزدیک | مهارت دستی | حساسیت به مسئله | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | وضوح گفتار | قدرت تنه | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | تقسیم توجه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | سپری کردن زمان در حالت ایستاده | داخل ساختمان، دارای کنترل محیطی | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | کار با یک گروه کاری یا تیم یا مشارکت در آن | سپری کردن زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوشت | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | سازندگان دسته‌ای مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و دسته‌بندها، محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی</t>
+          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش‌دادن فعال | سخن‌گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>تولید مواد غذایی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بینایی نزدیک | قدرت بالاتنه | چالاکی دست | ترتیب‌دهی اطلاعات | ثبات دست و بازو | تقسیم زمان | توجه انتخابی | حساسیت به مشکل | دقت کنترل | چالاکی انگشتان</t>
+          <t>درک شفاهی | بینایی نزدیک | قدرت تنه | مهارت دستی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | حساسیت به مسئله | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>سپری کردن زمان در حالت ایستاده | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | داخل ساختمان، دارای کنترل محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | کار با یک گروه کاری یا تیم یا مشارکت در آن | سپری کردن زمان برای انجام حرکات تکراری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوشت | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سازندگان دسته‌ای مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و دسته‌بندها، محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | پیشخدمت‌ها و گارسون‌ها</t>
+          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش‌دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | خدمات مشتریان و شخصی | زبان انگلیسی | تولید و فرآوری | امور اداری و مدیریت | آموزش و پرورش</t>
+          <t>تولید مواد غذایی | خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دستورالعمل‌های دستی | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت | بینایی نزدیک | بینایی دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مشکل | درک شفاهی | توجه انتخابی | بیان شفاهی | ترتیب‌دهی اطلاعات</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>سپری کردن زمان در حالت ایستاده | داخل ساختمان، بدون کنترل محیطی | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | اهمیت تکرار وظایف یکسان | سپری کردن زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | کار با یک گروه کاری یا تیم یا مشارکت در آن | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | سپری کردن زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارگران | پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات</t>
+          <t>صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آشپزها، رستوران | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، سفارش‌های فوری | آشپزها، فست فود | آشپزها، خانگی خصوصی | کارگران آماده‌سازی مواد غذایی | سرآشپزها و آشپزهای ارشد | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | نانوایان | قصابان و برش‌دهندگان گوشت | مدیران خدمات غذایی | بارتندرها | کارگران فست فود و پیشخوان | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | سروکنندگان غذا، غیررستورانی | پیشخدمت‌ها و گارسون‌ها | کارگران مرتبط با آماده‌سازی و سرو غذا، سایر موارد | سازندگان دسته‌ای مواد غذایی | تکنسین‌های رژیم غذایی</t>
+          <t>آشپزها، رستوران | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزها، سفارش‌های فوری | آشپزهای غذای آماده | آشپزهای خانگی خصوصی | کارگران آماده‌سازی مواد غذایی | سرآشپزها و آشپزهای ارشد | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | نانوایان | قصابان و برش‌دهندگان گوش | مدیران خدمات غذایی | بارتندرها | کارگران فست فود و پیشخوان | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | سروکنندگان غذا، غیررستورانی | پیشخدمت‌ها و گارسون‌ها | کارکنان آماده‌سازی و سرو غذا، سایر موارد | بچ‌سازان مواد غذایی | تکنسین‌های رژیم غذایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی</t>
+          <t>خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | قدرت بالاتنه | درک شفاهی</t>
+          <t>بینایی نزدیک | قدرت تنه | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>داخل ساختمان، دارای کنترل محیطی | سپری کردن زمان در حالت ایستاده | پوشیدن تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یک گروه کاری یا تیم یا مشارکت در آن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوشت | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | سازندگان دسته‌ای مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و دسته‌بندها، محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی</t>
+          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | تفکر انتقادی | مانیتورینگ | یادگیری فعال | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | آموزش و پرورش | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | چالاکی دست | ثبات دست و بازو | توجه انتخابی | حفظ کردن | استدلال استقرایی | استدلال قیاسی | حساسیت به مشکل | بیان کتبی | درک کتبی | توجه شنیداری | قدرت بالاتنه | چالاکی انگشتان</t>
+          <t>بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | مهارت دستی | ثبات دست و بازو | توجه انتخابی | حفظ کردن | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | درک کتبی | توجه شنیداری | قدرت تنه | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | سپری کردن زمان در حالت ایستاده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | داخل ساختمان، دارای کنترل محیطی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | اهمیت دقیق یا درست بودن | سپری کردن زمان برای انجام حرکات تکراری | سپری کردن زمان برای راه رفتن یا دویدن | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | کار با یک گروه کاری یا تیم یا مشارکت در آن</t>
+          <t>ارتباط با دیگران | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | فروشندگان خانه‌به‌خانه، فروشندگان خیابانی و روزنامه‌فروش‌ها و کارگران مرتبط | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبان‌ها و مهمان‌داران، رستوران، سالن و کافی‌شاپ | متصدیان رختکن و اتاق پرو | خدمتکاران و نظافتچی‌های خانه‌داری | پیشخدمت‌ها و گارسون‌ها</t>
+          <t>نانوایان | باریستاها | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | متصدیان رختکن، اتاق لباس و اتاق پرو | خدمتکاران و تمیزکنندگان خانه‌داری | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | تولید مواد غذایی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | کار با یک گروه کاری یا تیم یا مشارکت در آن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | سپری کردن زمان در حالت ایستاده | آزادی در تصمیم‌گیری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، دارای کنترل محیطی | سپری کردن زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | سپری کردن زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سپری کردن زمان برای خم شدن یا چرخاندن بدن | فراوانی تصمیم‌گیری</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای خم کردن یا چرخاندن بدن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | بارتندرها | قصابان و برش‌دهندگان گوشت | صندوق‌داران | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | سازندگان دسته‌ای مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبان‌ها و مهمان‌داران، رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها و گارسون‌ها</t>
+          <t>نانوایان | باریستاها | بارتندرها | قصابان و برش‌دهندگان گوش | صندوق‌داران | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | بچ‌سازان مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | مانیتورینگ | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | چالاکی انگشتان | ثبات دست و بازو | تقسیم زمان | ترتیب‌دهی اطلاعات | حساسیت به مشکل | درک کتبی | قدرت بالاتنه | دقت کنترل | چالاکی دست</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تقسیم توجه | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | قدرت تنه | دقت کنترل | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>سپری کردن زمان در حالت ایستاده | ارتباط با دیگران | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سپری کردن زمان برای انجام حرکات تکراری | کار با یک گروه کاری یا تیم یا مشارکت در آن | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | داخل ساختمان، دارای کنترل محیطی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | اهمیت دقیق یا درست بودن</t>
+          <t>صرف زمان برای ایستادن | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نانوایان | بارتندرها | قصابان و برش‌دهندگان گوشت | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | فروشندگان خانه‌به‌خانه، فروشندگان خیابانی و روزنامه‌فروش‌ها و کارگران مرتبط | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | میزبان‌ها و مهمان‌داران، رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها و گارسون‌ها</t>
+          <t>نانوایان | بارتندرها | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | میزبانان رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | مانیتورینگ</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تقسیم زمان | قدرت بالاتنه | استقامت | حساسیت به مشکل | چالاکی دست | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تقسیم توجه | قدرت تنه | استقامت | حساسیت به مسئله | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | سپری کردن زمان در حالت ایستاده | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سپری کردن زمان برای راه رفتن یا دویدن | کار با یک گروه کاری یا تیم یا مشارکت در آن | داخل ساختمان، دارای کنترل محیطی | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارگران | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سپری کردن زمان برای انجام حرکات تکراری | مکالمات تلفنی | اهمیت دقیق یا درست بودن</t>
+          <t>ارتباط با دیگران | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>باریستاها | بارتندرها | صندوق‌داران | سرآشپزها و آشپزهای ارشد | دربان‌ها | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا, غیررستورانی | مدیران خدمات غذایی | میزبان‌ها و مهمان‌داران، رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن و اتاق پرو</t>
+          <t>باریستاها | بارتندرها | صندوق‌داران | سرآشپزها و آشپزهای ارشد | کانسرج‌ها | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | گوش‌دادن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و شخصی | تولید مواد غذایی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>سپری کردن زمان در حالت ایستاده | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سپری کردن زمان برای راه رفتن یا دویدن | فشار زمانی | نزدیکی فیزیکی | کار با یک گروه کاری یا تیم یا مشارکت در آن | ارتباط با دیگران | سپری کردن زمان برای خم شدن یا چرخاندن بدن | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارگران | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارگران | سپری کردن زمان برای انجام حرکات تکراری | داخل ساختمان، دارای کنترل محیطی</t>
+          <t>صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای راه رفتن یا دویدن | فشار زمانی | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>باربران چمدان و پادوها | باریستاها | بارتندرها | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی مواد غذایی | مدیران خدمات غذایی | میزبان‌ها و مهمان‌داران، رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن و اتاق پرو | خدمتکاران و نظافتچی‌های خانه‌داری | پیشخدمت‌ها و گارسون‌ها</t>
+          <t>باربران چمدان و پادوهای هتل | باریستاها | بارتندرها | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارگران آماده‌سازی مواد غذایی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | خدمتکاران و تمیزکنندگان خانه‌داری | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | تولید مواد غذایی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | استقامت | چالاکی دست | ثبات دست و بازو | قدرت ایستا | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری گسترده</t>
+          <t>قدرت تنه | استقامت | مهارت دستی | ثبات دست و بازو | قدرت ایستا | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>سپری کردن زمان برای راه رفتن یا دویدن | سپری کردن زمان در حالت ایستاده | ارتباط با دیگران | کار با یک گروه کاری یا تیم یا مشارکت در آن | سپری کردن زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | سپری کردن زمان برای انجام حرکات تکراری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت دقیق یا درست بودن | داخل ساختمان، دارای کنترل محیطی | سپری کردن زمان برای خم شدن یا چرخاندن بدن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب</t>
+          <t>صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای خم کردن یا چرخاندن بدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>باربران چمدان و پادوها | باریستاها | بارتندرها | صندوق‌داران | سرآشپزها و آشپزهای ارشد | آشپزها، فست فود | آشپزها، موسسات و سلف‌سرویس‌ها | آشپزها، خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبان‌ها و مهمان‌داران، رستوران، سالن و کافی‌شاپ | متصدیان رختکن و اتاق پرو | خدمتکاران و نظافتچی‌های خانه‌داری | پیشخدمت‌ها و گارسون‌ها</t>
+          <t>باربران چمدان و پادوهای هتل | باریستاها | بارتندرها | صندوق‌داران | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | متصدیان رختکن، اتاق لباس و اتاق پرو | خدمتکاران و تمیزکنندگان خانه‌داری | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0057_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0057_fa.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | حساسیت به مسئله | توجه انتخابی | سرعت ادراک | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | تشخیص گفتار | تشخیص رنگ‌ها با چشم | وضوح گفتار | قدرت بالاتنه | دقت کنترل | چابکی انگشتان | ثبات دست و بازو | تسهیم زمان و توجه هم‌زمان</t>
+          <t>بینایی نزدیک | مهارت دستی | حساسیت به مسئله | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | تشخیص گفتار | تشخیص رنگ بصری | وضوح گفتار | قدرت تنه | دقت کنترل | مهارت انگشتان | ثبات دست و بازو | تقسیم توجه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | تولیدکنندگان دسته‌ای و صنعتی غذا | اپراتورها و مراقبان ماشین‌آلات پخت غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | اپراتورها و مراقبان ماشین‌آلات تفت‌دادن، پختن و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندان و دسته‌بندی‌کنندگان محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>تولید مواد غذایی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | قدرت بالاتنه | چابکی دستی | مرتب‌سازی اطلاعات | ثبات دست و بازو | تسهیم زمان و توجه هم‌زمان | توجه انتخابی | حساسیت به مسئله | دقت کنترل | چابکی انگشتان</t>
+          <t>درک شفاهی | بینایی نزدیک | قدرت تنه | مهارت دستی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | حساسیت به مسئله | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | تولیدکنندگان دسته‌ای و صنعتی غذا | اپراتورها و مراقبان ماشین‌آلات پخت غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | اپراتورها و مراقبان ماشین‌آلات تفت‌دادن، پختن و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندان و دسته‌بندی‌کنندگان محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | پیش‌خدمتان و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید و فراوری | مدیریت و امور اداری | آموزش و تدریس</t>
+          <t>تولید مواد غذایی | خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی میان‌اندام‌ها | دقت کنترل | قدرت ایستا | قدرت بالاتنه | استقامت جسمانی | دید نزدیک | دید دور | ادراک عمق | هماهنگی عمومی بدن | تعادل عمومی بدن | وسعت دامنه حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | مرتب‌سازی اطلاعات</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | بیان شفاهی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آشپزان رستوران | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان غذاهای فوری | آشپزان فست‌فود | آشپزان خانگی و شخصی | کارگران آماده‌سازی غذا | سرآشپزان و آشپزان ارشد | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | نانوایان | قصابان و خردکنندگان گوشت | مدیران خدمات پذیرایی و غذا | متصدیان بار و بارتندرها | کارگران پیشخوان و فست‌فود | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | سروکنندگان غذا در محیط‌های غیررستورانی | پیش‌خدمتان و گارسون‌ها | سایر کارکنان آماده‌سازی و سرو غذا | تولیدکنندگان دسته‌ای و صنعتی غذا | تکنسین‌های علوم تغذیه و رژیم‌درمانی</t>
+          <t>آشپزان رستوران | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان غذاهای فوری | آشپزان غذاهای فوری و فست‌فود | آشپزان منازل مسکونی و سرآشپزان شخصی | کارگران آماده‌سازی غذا | سرآشپزان و آشپزان ارشد | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | مدیران خدمات پذیرایی و غذا و نوشیدنی | متصدیان بار و نوشیدنی | کارگران پیشخوان و فست‌فود | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | سروکنندگان غذا در محیط‌های غیررستورانی | پیش‌خدمتان و گارسون‌ها | سایر کارکنان حوزه آماده‌سازی و ارائه غذا | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی</t>
+          <t>خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | قدرت بالاتنه | درک شفاهی</t>
+          <t>بینایی نزدیک | قدرت تنه | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | تولیدکنندگان دسته‌ای و صنعتی غذا | اپراتورها و مراقبان ماشین‌آلات پخت غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | اپراتورها و مراقبان ماشین‌آلات تفت‌دادن، پختن و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندان و دسته‌بندی‌کنندگان محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | چابکی دستی | ثبات دست و بازو | توجه انتخابی | به‌خاطرسپاری | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | درک کتبی | توجه شنیداری | قدرت بالاتنه | چابکی انگشتان</t>
+          <t>بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | مهارت دستی | ثبات دست و بازو | توجه انتخابی | حفظ کردن | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | درک کتبی | توجه شنیداری | قدرت تنه | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | فروشندگان دوره‌گرد، دکه‌داران و دست‌فروشان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | متصدیان رختکن، امانات و پرو لباس | نظافتچیان منازل و اماکن اقامتی | پیش‌خدمتان و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | بازاریابان حضوری و فروشندگان خیابانی | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان رختکن، امانات و اتاق پرو | خدمتکاران و نظافتچیان منازل و هتل‌ها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید مواد غذایی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>وضوح گفتار | تشخیص گفتار | دید نزدیک | بیان شفاهی | درک شفاهی</t>
+          <t>وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | متصدیان بار و بارتندرها | قصابان و خردکنندگان گوشت | صندوق‌داران | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | تولیدکنندگان دسته‌ای و صنعتی غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | متصدیان بار و نوشیدنی | قصابان و برش‌کاران گوشت | صندوق‌داران | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | چابکی انگشتان | ثبات دست و بازو | تسهیم زمان و توجه هم‌زمان | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک کتبی | قدرت بالاتنه | دقت کنترل | چابکی دستی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تقسیم توجه | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | قدرت تنه | دقت کنترل | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نانوایان | متصدیان بار و بارتندرها | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | فروشندگان دوره‌گرد، دکه‌داران و دست‌فروشان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | اپراتورها و مراقبان ماشین‌آلات تفت‌دادن، پختن و خشک‌کردن مواد غذایی و تنباکو | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | متصدیان بار و نوشیدنی | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | بازاریابان حضوری و فروشندگان خیابانی | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تسهیم زمان و توجه هم‌زمان | قدرت بالاتنه | استقامت جسمانی | حساسیت به مسئله | چابکی دستی | ثبات دست و بازو | استدلال قیاسی | مرتب‌سازی اطلاعات | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | تقسیم توجه | قدرت تنه | استقامت | حساسیت به مسئله | مهارت دستی | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>باریستاها | متصدیان بار و بارتندرها | صندوق‌داران | سرآشپزان و آشپزان ارشد | راهنمایان و مسئولان خدمات رفاهی و پذیرش مهمان (کانسیرژ) | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | متصدیان رختکن، امانات و پرو لباس</t>
+          <t>باریستاها | متصدیان بار و نوشیدنی | صندوق‌داران | سرآشپزان و آشپزان ارشد | متصدیان تشریفات و خدمات میهمانان | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | تولید مواد غذایی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>باربران و چمدان‌برهای هتل و مسافربری | باریستاها | متصدیان بار و بارتندرها | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | متصدیان رختکن، امانات و پرو لباس | نظافتچیان منازل و اماکن اقامتی | پیش‌خدمتان و گارسون‌ها</t>
+          <t>متصدیان حمل بار و خدمات هتل | باریستاها | متصدیان بار و نوشیدنی | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | خدمتکاران و نظافتچیان منازل و هتل‌ها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | زبان انگلیسی | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | زبان انگلیسی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | استقامت جسمانی | چابکی دستی | ثبات دست و بازو | قدرت ایستا | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | وسعت دامنه حرکتی</t>
+          <t>قدرت تنه | استقامت | مهارت دستی | ثبات دست و بازو | قدرت ایستا | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>باربران و چمدان‌برهای هتل و مسافربری | باریستاها | متصدیان بار و بارتندرها | صندوق‌داران | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز و سلف‌سرویس‌ها | آشپزان خانگی و شخصی | آشپزان رستوران | آشپزان غذاهای فوری | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا | میزبانان و پذیرش‌کنندگان رستوران، لانج و کافی‌شاپ | متصدیان رختکن، امانات و پرو لباس | نظافتچیان منازل و اماکن اقامتی | پیش‌خدمتان و گارسون‌ها</t>
+          <t>متصدیان حمل بار و خدمات هتل | باریستاها | متصدیان بار و نوشیدنی | صندوق‌داران | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان رختکن، امانات و اتاق پرو | خدمتکاران و نظافتچیان منازل و هتل‌ها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
